--- a/02_Zero_Shot/outputs/NLI/BART-large-MNLI/RESULT_pan_bart-large-mnli_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/NLI/BART-large-MNLI/RESULT_pan_bart-large-mnli_zeroshot.xlsx
@@ -24129,7 +24129,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4835525779473592</v>
+        <v>0.4835525779473593</v>
       </c>
     </row>
     <row r="5">
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67.41028181899947</v>
+        <v>95.59651325600134</v>
       </c>
     </row>
     <row r="8">
@@ -24169,7 +24169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04849660562517947</v>
+        <v>0.0687744699683463</v>
       </c>
     </row>
   </sheetData>
